--- a/data/raw/australiansuper_official.xlsx
+++ b/data/raw/australiansuper_official.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://australiansuper.sharepoint.com/teams/FO-FRSRI/PA/COMMUNICATION/Option Level Performance/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://australiansuper.sharepoint.com/teams/MEMMarketing/05_Member Commuications/Intermediary/Factsheets and posters/Monthly investment performance reports/2026/2026 09/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{997712A8-9C01-4629-B7D1-4B99C1476E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FEFF89B-52D8-4958-A6F2-0931E59F8E98}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{30A0CE51-3A2B-416B-9F57-D2E736E97DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20040B99-7903-4214-9937-2BA2690E4D67}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-60" windowWidth="29020" windowHeight="15700" tabRatio="682" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Superannuation" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
     <definedName name="wrn.Mid._.Month." hidden="1">{"PERFORMANCE",#N/A,FALSE,"Summary";"EQUITIES",#N/A,FALSE,"Equity";"Fixed Interest",#N/A,FALSE,"Fixed Interest";"Total Fund",#N/A,FALSE,"Total Fund"}</definedName>
     <definedName name="wrn.PACKAGE." hidden="1">{"PERFORMANCE",#N/A,FALSE,"Summary";"EQUITIES",#N/A,FALSE,"Equity";"FIXED INTEREST",#N/A,FALSE,"Fixed Interest";"RECONCILIATION",#N/A,FALSE,"Summary";"CROSS REFERENCE",#N/A,FALSE,"Summary"}</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -506,16 +506,7 @@
     </r>
   </si>
   <si>
-    <t>AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs, the percentage-based administration fee deducted from returns from 1 April 2020 to 2 September 2022 and taxes. Investment returns aren’t guaranteed. Past performance isn’t a reliable indicator of future returns. All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
-  </si>
-  <si>
-    <t>Returns from equivalent options of the ARF and STA super funds are used in calculating returns for periods that begin before 1 July 2006.</t>
-  </si>
-  <si>
-    <t>For TTR Income accounts, the investment return is based on the crediting rate for super (accumulation) options. From 1 April 2020 to 2 September 2022 the crediting rate includes an administration fee that was deducted from investment returns for super (accumulation) accounts. TTR Income accounts have been adjusted to refund the administration fee deducted from investment returns.</t>
-  </si>
-  <si>
-    <t>Report generated on 02 September 2026</t>
+    <t>Investment returns are not guaranteed. Past performance is not a reliable indicator of future returns.  All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
   </si>
   <si>
     <r>
@@ -595,9 +586,6 @@
   </si>
   <si>
     <t>Choice Income AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs and taxes.</t>
-  </si>
-  <si>
-    <t>Investment returns are not guaranteed. Past performance is not a reliable indicator of future returns.  All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
   </si>
   <si>
     <r>
@@ -661,6 +649,18 @@
       <t>. AustralianSuper Pty Ltd, ABN 94 006 457 987, AFSL 233788, Trustee of AustralianSuper ABN 65 714 394 898.</t>
     </r>
   </si>
+  <si>
+    <t>AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs, the percentage-based administration fee deducted from returns from 1 April 2020 to 2 September 2022 and taxes. Investment returns aren’t guaranteed. Past performance isn’t a reliable indicator of future returns. All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
+  </si>
+  <si>
+    <t>Returns from equivalent options of the ARF and STA super funds are used in calculating returns for periods that begin before 1 July 2006.</t>
+  </si>
+  <si>
+    <t>For TTR Income accounts, the investment return is based on the crediting rate for super (accumulation) options. From 1 April 2020 to 2 September 2022 the crediting rate includes an administration fee that was deducted from investment returns for super (accumulation) accounts. TTR Income accounts have been adjusted to refund the administration fee deducted from investment returns.</t>
+  </si>
+  <si>
+    <t>Report generated on 02 October 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -673,7 +673,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -749,6 +749,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1015,19 +1021,19 @@
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1043,6 +1049,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1052,19 +1061,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1076,10 +1085,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1088,13 +1097,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1115,7 +1124,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1130,13 +1139,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1256,7 +1265,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1349,56 +1358,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>39780</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>145677</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>643030</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>193061</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78F988E7-677B-8841-919F-1F33FC364FD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="39780" y="145677"/>
-          <a:ext cx="12734925" cy="2564972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1485,30 +1444,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>25399</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>124883</xdr:rowOff>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>14111</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>15616</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>106868</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50EDC577-1CB3-B348-ADA7-918DF52B55A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572E5778-5D7C-41CD-AE7D-7DCB8C2BA238}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1517,21 +1471,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25399" y="287161"/>
-          <a:ext cx="11969045" cy="2331485"/>
+          <a:off x="152400" y="36286"/>
+          <a:ext cx="12635787" cy="2603500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1540,6 +1493,108 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>206829</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1097643</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10702929" cy="928703"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB85BE68-1ABC-4F8E-BF58-D8C7FDE55564}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="206829" y="1260929"/>
+          <a:ext cx="10702929" cy="928703"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="118872" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Superannuation In</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>vestment performance</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Performance to 30 September 2026</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1661,6 +1716,152 @@
             <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>77611</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>56445</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28222</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>148167</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4056C889-C98B-4C23-A152-03F850AB3BA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="317500" y="56445"/>
+          <a:ext cx="11691055" cy="2603500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>176390</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>846666</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10702929" cy="928703"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F413CF4-1CD7-42C4-BD0A-63ACD717EDC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="416279" y="1008944"/>
+          <a:ext cx="10702929" cy="928703"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="118872" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Choice Income In</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>vestment performance</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Performance to 30 September 2026</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1960,1143 +2161,1169 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
-  <sheetFormatPr defaultColWidth="7.1640625" defaultRowHeight="12.95"/>
+  <dimension ref="A1:X39"/>
+  <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="12" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="13" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.296875" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="18" width="11.33203125" customWidth="1"/>
-    <col min="19" max="19" width="3.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.796875" customWidth="1"/>
+    <col min="5" max="18" width="11.296875" customWidth="1"/>
+    <col min="19" max="19" width="3.19921875" customWidth="1"/>
+    <col min="21" max="21" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" hidden="1">
-      <c r="C1" s="10">
-        <v>46265</v>
-      </c>
-      <c r="D1" s="10" t="s">
+    <row r="1" spans="1:24" ht="13" hidden="1" customHeight="1">
+      <c r="C1" s="11">
+        <v>46295</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-    </row>
-    <row r="2" spans="1:22" hidden="1">
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-    </row>
-    <row r="4" spans="1:22" ht="95.1" customHeight="1"/>
-    <row r="5" spans="1:22" ht="71.099999999999994" customHeight="1">
-      <c r="B5" s="12"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-    </row>
-    <row r="6" spans="1:22" ht="18.95" customHeight="1">
-      <c r="B6" s="12"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-    </row>
-    <row r="7" spans="1:22" ht="18" customHeight="1">
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-    </row>
-    <row r="8" spans="1:22" ht="21">
-      <c r="C8" s="5" t="s">
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+    </row>
+    <row r="2" spans="1:24" hidden="1">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+    </row>
+    <row r="4" spans="1:24" ht="95.15" customHeight="1"/>
+    <row r="5" spans="1:24" ht="71.150000000000006" customHeight="1">
+      <c r="B5" s="13"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+    </row>
+    <row r="6" spans="1:24" ht="19" customHeight="1">
+      <c r="B6" s="13"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+    </row>
+    <row r="7" spans="1:24" ht="18" customHeight="1">
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+    </row>
+    <row r="8" spans="1:24" ht="21">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="72" t="s">
+      <c r="Q8" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="72"/>
-    </row>
-    <row r="9" spans="1:22" s="30" customFormat="1">
-      <c r="A9" s="29"/>
-      <c r="C9" s="31" t="s">
+      <c r="R8" s="73"/>
+    </row>
+    <row r="9" spans="1:24" s="31" customFormat="1">
+      <c r="A9" s="30"/>
+      <c r="C9" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9"/>
-    </row>
-    <row r="10" spans="1:22" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="W9"/>
+      <c r="X9"/>
+    </row>
+    <row r="10" spans="1:24" ht="12.75" customHeight="1">
+      <c r="A10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="52">
-        <v>53601.594668620004</v>
-      </c>
-      <c r="E10" s="53">
-        <v>1.2069804911630705E-2</v>
-      </c>
-      <c r="F10" s="53">
-        <v>3.1107157199089599E-2</v>
-      </c>
-      <c r="G10" s="53">
-        <v>4.6308420471095346E-2</v>
-      </c>
-      <c r="H10" s="53">
-        <v>1.7953652579422899E-2</v>
-      </c>
-      <c r="I10" s="53">
-        <v>0.10084068534033083</v>
-      </c>
-      <c r="J10" s="53">
-        <v>0.10806992620060404</v>
-      </c>
-      <c r="K10" s="53">
-        <v>0.10802014356003435</v>
-      </c>
-      <c r="L10" s="53">
-        <v>7.3243572815313268E-2</v>
-      </c>
-      <c r="M10" s="53">
-        <v>8.8801714222398492E-2</v>
-      </c>
-      <c r="N10" s="53">
-        <v>9.4306812121162681E-2</v>
-      </c>
-      <c r="O10" s="53">
-        <v>0.10053832924624047</v>
-      </c>
-      <c r="P10" s="53">
-        <v>7.7173477555743206E-2</v>
-      </c>
-      <c r="Q10" s="53">
-        <v>8.5021284125941135E-2</v>
-      </c>
-      <c r="R10" s="41">
+      <c r="D10" s="53">
+        <v>53639.247382589994</v>
+      </c>
+      <c r="E10" s="54">
+        <v>-6.7689437702521758E-3</v>
+      </c>
+      <c r="F10" s="54">
+        <v>1.1063181544389969E-2</v>
+      </c>
+      <c r="G10" s="54">
+        <v>7.986137475012127E-2</v>
+      </c>
+      <c r="H10" s="54">
+        <v>1.1063181544389969E-2</v>
+      </c>
+      <c r="I10" s="54">
+        <v>7.9989517948012068E-2</v>
+      </c>
+      <c r="J10" s="54">
+        <v>9.9348763743442245E-2</v>
+      </c>
+      <c r="K10" s="54">
+        <v>0.11223226586334464</v>
+      </c>
+      <c r="L10" s="54">
+        <v>7.4801297931077787E-2</v>
+      </c>
+      <c r="M10" s="54">
+        <v>8.6058271490858596E-2</v>
+      </c>
+      <c r="N10" s="54">
+        <v>9.3132789432411558E-2</v>
+      </c>
+      <c r="O10" s="54">
+        <v>0.10202782061088164</v>
+      </c>
+      <c r="P10" s="54">
+        <v>7.5989427389306557E-2</v>
+      </c>
+      <c r="Q10" s="54">
+        <v>8.4537551213690137E-2</v>
+      </c>
+      <c r="R10" s="42">
         <v>35247</v>
       </c>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-    </row>
-    <row r="11" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+    </row>
+    <row r="11" spans="1:24" ht="13" customHeight="1">
+      <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="46">
-        <v>268148.02426069003</v>
-      </c>
-      <c r="E11" s="47">
-        <v>9.162464459985524E-3</v>
-      </c>
-      <c r="F11" s="47">
-        <v>2.6629480686595656E-2</v>
-      </c>
-      <c r="G11" s="47">
-        <v>3.971164337832031E-2</v>
-      </c>
-      <c r="H11" s="47">
-        <v>1.298328778207432E-2</v>
-      </c>
-      <c r="I11" s="47">
-        <v>8.4458936294144027E-2</v>
-      </c>
-      <c r="J11" s="47">
-        <v>9.1785084834094796E-2</v>
-      </c>
-      <c r="K11" s="47">
-        <v>9.1877403073721844E-2</v>
-      </c>
-      <c r="L11" s="47">
-        <v>6.2544109892306771E-2</v>
-      </c>
-      <c r="M11" s="47">
-        <v>7.504774225986531E-2</v>
-      </c>
-      <c r="N11" s="47">
-        <v>8.2670942551451548E-2</v>
-      </c>
-      <c r="O11" s="47">
-        <v>8.9701227921958115E-2</v>
-      </c>
-      <c r="P11" s="47">
-        <v>7.2771959794668994E-2</v>
-      </c>
-      <c r="Q11" s="47">
-        <v>9.2740098643259994E-2</v>
-      </c>
-      <c r="R11" s="24">
+      <c r="D11" s="47">
+        <v>266375.86592970998</v>
+      </c>
+      <c r="E11" s="48">
+        <v>-5.3686642612352491E-3</v>
+      </c>
+      <c r="F11" s="48">
+        <v>7.5449206077301163E-3</v>
+      </c>
+      <c r="G11" s="48">
+        <v>6.6346498717247987E-2</v>
+      </c>
+      <c r="H11" s="48">
+        <v>7.5449206077301163E-3</v>
+      </c>
+      <c r="I11" s="48">
+        <v>6.7024963046260155E-2</v>
+      </c>
+      <c r="J11" s="48">
+        <v>8.406677633198234E-2</v>
+      </c>
+      <c r="K11" s="48">
+        <v>9.5530689494419757E-2</v>
+      </c>
+      <c r="L11" s="48">
+        <v>6.329331211820069E-2</v>
+      </c>
+      <c r="M11" s="48">
+        <v>7.2932870262985963E-2</v>
+      </c>
+      <c r="N11" s="48">
+        <v>8.1679100483851463E-2</v>
+      </c>
+      <c r="O11" s="48">
+        <v>9.073213428085268E-2</v>
+      </c>
+      <c r="P11" s="48">
+        <v>7.1803900366588361E-2</v>
+      </c>
+      <c r="Q11" s="48">
+        <v>9.2403992988553979E-2</v>
+      </c>
+      <c r="R11" s="25">
         <v>31260</v>
       </c>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-    </row>
-    <row r="12" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A12" s="12" t="s">
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+    </row>
+    <row r="12" spans="1:24" ht="13" customHeight="1">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="48">
-        <v>3221.7452449299999</v>
-      </c>
-      <c r="E12" s="49">
-        <v>7.9440546448471816E-3</v>
-      </c>
-      <c r="F12" s="49">
-        <v>2.4794610377640407E-2</v>
-      </c>
-      <c r="G12" s="49">
-        <v>3.5356136564457866E-2</v>
-      </c>
-      <c r="H12" s="49">
-        <v>6.3700421781682131E-3</v>
-      </c>
-      <c r="I12" s="49">
-        <v>7.1168626177624664E-2</v>
-      </c>
-      <c r="J12" s="49">
-        <v>8.4316360242061364E-2</v>
-      </c>
-      <c r="K12" s="49">
-        <v>8.9327457651450226E-2</v>
-      </c>
-      <c r="L12" s="49">
-        <v>5.6582015416038522E-2</v>
-      </c>
-      <c r="M12" s="49">
-        <v>6.706720981647829E-2</v>
-      </c>
-      <c r="N12" s="49">
-        <v>7.3592220624871349E-2</v>
-      </c>
-      <c r="O12" s="49">
-        <v>8.4755166567765328E-2</v>
-      </c>
-      <c r="P12" s="49">
-        <v>6.9152438160794291E-2</v>
-      </c>
-      <c r="Q12" s="49">
-        <v>7.0399882577276751E-2</v>
-      </c>
-      <c r="R12" s="25">
+      <c r="D12" s="49">
+        <v>3162.8207158699997</v>
+      </c>
+      <c r="E12" s="50">
+        <v>-1.0987298046276947E-2</v>
+      </c>
+      <c r="F12" s="50">
+        <v>-4.6872454200876231E-3</v>
+      </c>
+      <c r="G12" s="50">
+        <v>7.2195837323352552E-2</v>
+      </c>
+      <c r="H12" s="50">
+        <v>-4.6872454200876231E-3</v>
+      </c>
+      <c r="I12" s="50">
+        <v>4.7143333856115979E-2</v>
+      </c>
+      <c r="J12" s="50">
+        <v>7.4485623601465586E-2</v>
+      </c>
+      <c r="K12" s="50">
+        <v>9.1994529116318308E-2</v>
+      </c>
+      <c r="L12" s="50">
+        <v>5.6289909189991827E-2</v>
+      </c>
+      <c r="M12" s="50">
+        <v>6.3711126459218767E-2</v>
+      </c>
+      <c r="N12" s="50">
+        <v>7.2248329191129071E-2</v>
+      </c>
+      <c r="O12" s="50">
+        <v>8.4955820001787821E-2</v>
+      </c>
+      <c r="P12" s="50">
+        <v>6.8199938296431478E-2</v>
+      </c>
+      <c r="Q12" s="50">
+        <v>6.9688137860366442E-2</v>
+      </c>
+      <c r="R12" s="26">
         <v>37165</v>
       </c>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-    </row>
-    <row r="13" spans="1:22" ht="12.6" customHeight="1">
-      <c r="A13" s="12" t="s">
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+    </row>
+    <row r="13" spans="1:24" ht="12.65" customHeight="1">
+      <c r="A13" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="46">
-        <v>4697.6287786700004</v>
-      </c>
-      <c r="E13" s="47">
-        <v>8.386804045988426E-3</v>
-      </c>
-      <c r="F13" s="47">
-        <v>2.3314538736661432E-2</v>
-      </c>
-      <c r="G13" s="47">
-        <v>3.7960116402691188E-2</v>
-      </c>
-      <c r="H13" s="47">
-        <v>1.099298426620271E-2</v>
-      </c>
-      <c r="I13" s="47">
-        <v>6.9914675015194494E-2</v>
-      </c>
-      <c r="J13" s="47">
-        <v>9.533511368307919E-2</v>
-      </c>
-      <c r="K13" s="47">
-        <v>0.10522551412102861</v>
-      </c>
-      <c r="L13" s="47">
-        <v>6.9027203936041934E-2</v>
-      </c>
-      <c r="M13" s="47">
-        <v>7.9802326933586035E-2</v>
-      </c>
-      <c r="N13" s="47">
-        <v>8.0701443603471743E-2</v>
-      </c>
-      <c r="O13" s="47">
-        <v>8.0694702992322495E-2</v>
-      </c>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47">
-        <v>7.7137317431364219E-2</v>
-      </c>
-      <c r="R13" s="26">
+      <c r="D13" s="47">
+        <v>4706.8597366200001</v>
+      </c>
+      <c r="E13" s="48">
+        <v>-3.626826826081923E-3</v>
+      </c>
+      <c r="F13" s="48">
+        <v>7.3262877898854278E-3</v>
+      </c>
+      <c r="G13" s="48">
+        <v>7.4293422579963617E-2</v>
+      </c>
+      <c r="H13" s="48">
+        <v>7.3262877898854278E-3</v>
+      </c>
+      <c r="I13" s="48">
+        <v>5.7501248791940983E-2</v>
+      </c>
+      <c r="J13" s="48">
+        <v>8.7241889678019338E-2</v>
+      </c>
+      <c r="K13" s="48">
+        <v>0.11232402038459013</v>
+      </c>
+      <c r="L13" s="48">
+        <v>7.197666879513874E-2</v>
+      </c>
+      <c r="M13" s="48">
+        <v>7.7284602815255093E-2</v>
+      </c>
+      <c r="N13" s="48">
+        <v>8.0697359282553269E-2</v>
+      </c>
+      <c r="O13" s="48">
+        <v>8.2619006845751589E-2</v>
+      </c>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48">
+        <v>7.6450109119220441E-2</v>
+      </c>
+      <c r="R13" s="27">
         <v>40725</v>
       </c>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-    </row>
-    <row r="14" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+    </row>
+    <row r="14" spans="1:24" ht="13" customHeight="1">
+      <c r="A14" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="48">
-        <v>7442.6599516400001</v>
-      </c>
-      <c r="E14" s="49">
-        <v>7.0561312210485044E-3</v>
-      </c>
-      <c r="F14" s="49">
-        <v>2.167445252899991E-2</v>
-      </c>
-      <c r="G14" s="49">
-        <v>3.3057132660072444E-2</v>
-      </c>
-      <c r="H14" s="49">
-        <v>9.3652303587481653E-3</v>
-      </c>
-      <c r="I14" s="49">
-        <v>7.0384738820875356E-2</v>
-      </c>
-      <c r="J14" s="49">
-        <v>7.7907869585484568E-2</v>
-      </c>
-      <c r="K14" s="49">
-        <v>7.6598087394635028E-2</v>
-      </c>
-      <c r="L14" s="49">
-        <v>4.8682248797090419E-2</v>
-      </c>
-      <c r="M14" s="49">
-        <v>5.7126574011870004E-2</v>
-      </c>
-      <c r="N14" s="49">
-        <v>6.3910229583729897E-2</v>
-      </c>
-      <c r="O14" s="49">
-        <v>7.2756932281311165E-2</v>
-      </c>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49">
-        <v>5.946031576820391E-2</v>
-      </c>
-      <c r="R14" s="25">
+      <c r="D14" s="49">
+        <v>7361.3225265699994</v>
+      </c>
+      <c r="E14" s="50">
+        <v>-5.2802841263404196E-3</v>
+      </c>
+      <c r="F14" s="50">
+        <v>4.0354951552049262E-3</v>
+      </c>
+      <c r="G14" s="50">
+        <v>5.3406969061974077E-2</v>
+      </c>
+      <c r="H14" s="50">
+        <v>4.0354951552049262E-3</v>
+      </c>
+      <c r="I14" s="50">
+        <v>5.4691975284177824E-2</v>
+      </c>
+      <c r="J14" s="50">
+        <v>7.0963394890794368E-2</v>
+      </c>
+      <c r="K14" s="50">
+        <v>7.9227396311469966E-2</v>
+      </c>
+      <c r="L14" s="50">
+        <v>4.9186775239584618E-2</v>
+      </c>
+      <c r="M14" s="50">
+        <v>5.5547136825096217E-2</v>
+      </c>
+      <c r="N14" s="50">
+        <v>6.3006872869494454E-2</v>
+      </c>
+      <c r="O14" s="50">
+        <v>7.3383263401048435E-2</v>
+      </c>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50">
+        <v>5.8903341245256105E-2</v>
+      </c>
+      <c r="R14" s="26">
         <v>39326</v>
       </c>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-    </row>
-    <row r="15" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+    </row>
+    <row r="15" spans="1:24" ht="13" customHeight="1">
+      <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="50">
-        <v>4777.0241783199999</v>
-      </c>
-      <c r="E15" s="51">
-        <v>4.4162747860181121E-3</v>
-      </c>
-      <c r="F15" s="51">
-        <v>1.4537097563388245E-2</v>
-      </c>
-      <c r="G15" s="51">
-        <v>2.259763156150758E-2</v>
-      </c>
-      <c r="H15" s="51">
-        <v>5.1433398205637127E-3</v>
-      </c>
-      <c r="I15" s="51">
-        <v>5.2460855012208471E-2</v>
-      </c>
-      <c r="J15" s="51">
-        <v>6.038254795428033E-2</v>
-      </c>
-      <c r="K15" s="51">
-        <v>5.8955594102952133E-2</v>
-      </c>
-      <c r="L15" s="51">
-        <v>3.5866414471040539E-2</v>
-      </c>
-      <c r="M15" s="51">
-        <v>3.964113742930378E-2</v>
-      </c>
-      <c r="N15" s="51">
-        <v>4.7124863259804875E-2</v>
-      </c>
-      <c r="O15" s="51">
-        <v>5.5984145086340038E-2</v>
-      </c>
-      <c r="P15" s="51">
-        <v>5.373811231809416E-2</v>
-      </c>
-      <c r="Q15" s="51">
-        <v>5.7920124424838237E-2</v>
-      </c>
-      <c r="R15" s="27">
+      <c r="D15" s="51">
+        <v>4763.9124636000006</v>
+      </c>
+      <c r="E15" s="52">
+        <v>-5.6115772321522822E-3</v>
+      </c>
+      <c r="F15" s="52">
+        <v>-4.9709966022286681E-4</v>
+      </c>
+      <c r="G15" s="52">
+        <v>3.5521270921550226E-2</v>
+      </c>
+      <c r="H15" s="52">
+        <v>-4.9709966022286681E-4</v>
+      </c>
+      <c r="I15" s="52">
+        <v>3.8598571450287146E-2</v>
+      </c>
+      <c r="J15" s="52">
+        <v>5.3994634375172733E-2</v>
+      </c>
+      <c r="K15" s="52">
+        <v>6.0434266597849597E-2</v>
+      </c>
+      <c r="L15" s="52">
+        <v>3.5564625485420283E-2</v>
+      </c>
+      <c r="M15" s="52">
+        <v>3.8438010268578411E-2</v>
+      </c>
+      <c r="N15" s="52">
+        <v>4.6253683463863472E-2</v>
+      </c>
+      <c r="O15" s="52">
+        <v>5.5896960955653191E-2</v>
+      </c>
+      <c r="P15" s="52">
+        <v>5.3295227731681862E-2</v>
+      </c>
+      <c r="Q15" s="52">
+        <v>5.7486532187757587E-2</v>
+      </c>
+      <c r="R15" s="28">
         <v>37165</v>
       </c>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-    </row>
-    <row r="16" spans="1:22" s="30" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A16" s="29"/>
-      <c r="C16" s="31" t="s">
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+    </row>
+    <row r="16" spans="1:24" s="31" customFormat="1" ht="16" customHeight="1">
+      <c r="A16" s="30"/>
+      <c r="C16" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="33"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-    </row>
-    <row r="17" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A17" s="12" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="34"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="39"/>
+    </row>
+    <row r="17" spans="1:24" ht="13" customHeight="1">
+      <c r="A17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="52">
-        <v>9874.6126533400002</v>
-      </c>
-      <c r="E17" s="53">
-        <v>2.2136898126383527E-2</v>
-      </c>
-      <c r="F17" s="53">
-        <v>4.5360714569344783E-2</v>
-      </c>
-      <c r="G17" s="53">
-        <v>1.7552240501722622E-2</v>
-      </c>
-      <c r="H17" s="53">
-        <v>4.1301835948344329E-2</v>
-      </c>
-      <c r="I17" s="53">
-        <v>9.4757916918292898E-2</v>
-      </c>
-      <c r="J17" s="53">
-        <v>0.11650402317063017</v>
-      </c>
-      <c r="K17" s="53">
-        <v>0.12488000895287715</v>
-      </c>
-      <c r="L17" s="53">
-        <v>9.7655256847581917E-2</v>
-      </c>
-      <c r="M17" s="53">
-        <v>0.10205545453941973</v>
-      </c>
-      <c r="N17" s="53">
-        <v>0.10468888693948324</v>
-      </c>
-      <c r="O17" s="53">
-        <v>0.10634624135041164</v>
-      </c>
-      <c r="P17" s="53">
-        <v>8.3319686142458868E-2</v>
-      </c>
-      <c r="Q17" s="53">
-        <v>9.696799730364157E-2</v>
-      </c>
-      <c r="R17" s="55">
+      <c r="D17" s="53">
+        <v>9552.2901939799995</v>
+      </c>
+      <c r="E17" s="54">
+        <v>-3.0888769169793346E-2</v>
+      </c>
+      <c r="F17" s="54">
+        <v>9.1373039016539037E-3</v>
+      </c>
+      <c r="G17" s="54">
+        <v>4.5414119405527031E-2</v>
+      </c>
+      <c r="H17" s="54">
+        <v>9.1373039016539037E-3</v>
+      </c>
+      <c r="I17" s="54">
+        <v>6.0237341941267848E-2</v>
+      </c>
+      <c r="J17" s="54">
+        <v>8.5300518442162937E-2</v>
+      </c>
+      <c r="K17" s="54">
+        <v>0.12084098281890408</v>
+      </c>
+      <c r="L17" s="54">
+        <v>9.3384079085947078E-2</v>
+      </c>
+      <c r="M17" s="54">
+        <v>9.3851752430353319E-2</v>
+      </c>
+      <c r="N17" s="54">
+        <v>0.10023720775394324</v>
+      </c>
+      <c r="O17" s="54">
+        <v>0.1081797696877458</v>
+      </c>
+      <c r="P17" s="54">
+        <v>8.1054842406161814E-2</v>
+      </c>
+      <c r="Q17" s="54">
+        <v>9.5386454813341487E-2</v>
+      </c>
+      <c r="R17" s="56">
         <v>36434</v>
       </c>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-    </row>
-    <row r="18" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="39"/>
+      <c r="X17" s="39"/>
+    </row>
+    <row r="18" spans="1:24" ht="13" customHeight="1">
+      <c r="A18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="56">
-        <v>11594.549893670001</v>
-      </c>
-      <c r="E18" s="57">
-        <v>3.1448730938107342E-3</v>
-      </c>
-      <c r="F18" s="57">
-        <v>2.8993968174692703E-2</v>
-      </c>
-      <c r="G18" s="57">
-        <v>8.0486577247439933E-2</v>
-      </c>
-      <c r="H18" s="57">
-        <v>-2.0610556811300421E-3</v>
-      </c>
-      <c r="I18" s="57">
-        <v>0.10213057789125175</v>
-      </c>
-      <c r="J18" s="57">
-        <v>0.13290584219204477</v>
-      </c>
-      <c r="K18" s="57">
-        <v>0.14020330572971745</v>
-      </c>
-      <c r="L18" s="57">
-        <v>8.41529153538213E-2</v>
-      </c>
-      <c r="M18" s="57">
-        <v>0.11692665051334461</v>
-      </c>
-      <c r="N18" s="57">
-        <v>0.12060952585514001</v>
-      </c>
-      <c r="O18" s="57">
-        <v>0.12808424657977008</v>
-      </c>
-      <c r="P18" s="57">
-        <v>8.2989837486609458E-2</v>
-      </c>
-      <c r="Q18" s="57">
-        <v>7.1218041190505121E-2</v>
-      </c>
-      <c r="R18" s="44">
+      <c r="D18" s="57">
+        <v>11828.396820739999</v>
+      </c>
+      <c r="E18" s="58">
+        <v>1.5924703537953413E-2</v>
+      </c>
+      <c r="F18" s="58">
+        <v>1.383082615612616E-2</v>
+      </c>
+      <c r="G18" s="58">
+        <v>0.138022295138197</v>
+      </c>
+      <c r="H18" s="58">
+        <v>1.383082615612616E-2</v>
+      </c>
+      <c r="I18" s="58">
+        <v>9.7250102967643512E-2</v>
+      </c>
+      <c r="J18" s="58">
+        <v>0.14560107663797614</v>
+      </c>
+      <c r="K18" s="58">
+        <v>0.15986074628126862</v>
+      </c>
+      <c r="L18" s="58">
+        <v>9.3921448412911321E-2</v>
+      </c>
+      <c r="M18" s="58">
+        <v>0.11853401549729009</v>
+      </c>
+      <c r="N18" s="58">
+        <v>0.12314802238752859</v>
+      </c>
+      <c r="O18" s="58">
+        <v>0.13000107803215172</v>
+      </c>
+      <c r="P18" s="58">
+        <v>8.2334016173504526E-2</v>
+      </c>
+      <c r="Q18" s="58">
+        <v>7.1620320989854228E-2</v>
+      </c>
+      <c r="R18" s="45">
         <v>36434</v>
       </c>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-    </row>
-    <row r="19" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A19" s="12" t="s">
+      <c r="U18" s="39"/>
+      <c r="V18" s="39"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+    </row>
+    <row r="19" spans="1:24" ht="13" customHeight="1">
+      <c r="A19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="64" t="s">
+      <c r="C19" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="58">
-        <v>1267.9132201800001</v>
-      </c>
-      <c r="E19" s="59">
-        <v>8.1951431261101927E-7</v>
-      </c>
-      <c r="F19" s="59">
-        <v>3.65296263975877E-4</v>
-      </c>
-      <c r="G19" s="59">
-        <v>-2.9899154902737588E-3</v>
-      </c>
-      <c r="H19" s="59">
-        <v>-6.0552866260875395E-3</v>
-      </c>
-      <c r="I19" s="59">
-        <v>1.2188512906191775E-2</v>
-      </c>
-      <c r="J19" s="59">
-        <v>2.3305133676518951E-2</v>
-      </c>
-      <c r="K19" s="59">
-        <v>2.8811001684989377E-2</v>
-      </c>
-      <c r="L19" s="59">
-        <v>8.356386881523032E-3</v>
-      </c>
-      <c r="M19" s="59">
-        <v>9.2060359403775705E-3</v>
-      </c>
-      <c r="N19" s="59">
-        <v>1.7951062174197563E-2</v>
-      </c>
-      <c r="O19" s="59">
-        <v>3.3518849760306106E-2</v>
-      </c>
-      <c r="P19" s="59">
-        <v>4.0605101168462616E-2</v>
-      </c>
-      <c r="Q19" s="59">
-        <v>4.6506865724591132E-2</v>
-      </c>
-      <c r="R19" s="43">
+      <c r="D19" s="59">
+        <v>1244.2471929400001</v>
+      </c>
+      <c r="E19" s="60">
+        <v>-1.116527747892216E-2</v>
+      </c>
+      <c r="F19" s="60">
+        <v>-1.7152955149615026E-2</v>
+      </c>
+      <c r="G19" s="60">
+        <v>1.1663300764757905E-3</v>
+      </c>
+      <c r="H19" s="60">
+        <v>-1.7152955149615026E-2</v>
+      </c>
+      <c r="I19" s="60">
+        <v>-2.6532488318756309E-3</v>
+      </c>
+      <c r="J19" s="60">
+        <v>1.5369920823321009E-2</v>
+      </c>
+      <c r="K19" s="60">
+        <v>2.6088584456489983E-2</v>
+      </c>
+      <c r="L19" s="60">
+        <v>5.9025620385552103E-3</v>
+      </c>
+      <c r="M19" s="60">
+        <v>7.858947411154546E-3</v>
+      </c>
+      <c r="N19" s="60">
+        <v>1.6619151075572568E-2</v>
+      </c>
+      <c r="O19" s="60">
+        <v>3.1569666198125443E-2</v>
+      </c>
+      <c r="P19" s="60">
+        <v>3.9730690693313309E-2</v>
+      </c>
+      <c r="Q19" s="60">
+        <v>4.5932781479145181E-2</v>
+      </c>
+      <c r="R19" s="44">
         <v>36342</v>
       </c>
-      <c r="U19" s="38"/>
-      <c r="V19" s="38"/>
-    </row>
-    <row r="20" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A20" s="12" t="s">
+      <c r="U19" s="39"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="39"/>
+    </row>
+    <row r="20" spans="1:24" ht="13" customHeight="1">
+      <c r="A20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="60">
-        <v>8280.2863877100008</v>
-      </c>
-      <c r="E20" s="61">
-        <v>3.6562350592770844E-3</v>
-      </c>
-      <c r="F20" s="61">
-        <v>1.1289870588666089E-2</v>
-      </c>
-      <c r="G20" s="61">
-        <v>2.0992786907660561E-2</v>
-      </c>
-      <c r="H20" s="61">
-        <v>7.5161529423916707E-3</v>
-      </c>
-      <c r="I20" s="61">
-        <v>3.9061015880249718E-2</v>
-      </c>
-      <c r="J20" s="61">
-        <v>4.0431549033541098E-2</v>
-      </c>
-      <c r="K20" s="61">
-        <v>4.0591068773476659E-2</v>
-      </c>
-      <c r="L20" s="61">
-        <v>3.1278799832963201E-2</v>
-      </c>
-      <c r="M20" s="61">
-        <v>2.3625464100176508E-2</v>
-      </c>
-      <c r="N20" s="61">
-        <v>2.2226942310058832E-2</v>
-      </c>
-      <c r="O20" s="61">
-        <v>2.4344475140603953E-2</v>
-      </c>
-      <c r="P20" s="61">
-        <v>3.0841203846075957E-2</v>
-      </c>
-      <c r="Q20" s="61">
-        <v>3.4361068037941526E-2</v>
-      </c>
-      <c r="R20" s="62">
+      <c r="D20" s="61">
+        <v>8535.0704452700011</v>
+      </c>
+      <c r="E20" s="62">
+        <v>3.3081293886744294E-3</v>
+      </c>
+      <c r="F20" s="62">
+        <v>1.0849146737504598E-2</v>
+      </c>
+      <c r="G20" s="62">
+        <v>2.1402311036106035E-2</v>
+      </c>
+      <c r="H20" s="62">
+        <v>1.0849146737504598E-2</v>
+      </c>
+      <c r="I20" s="62">
+        <v>3.9302110751960766E-2</v>
+      </c>
+      <c r="J20" s="62">
+        <v>4.0387899699764217E-2</v>
+      </c>
+      <c r="K20" s="62">
+        <v>4.0670419005259105E-2</v>
+      </c>
+      <c r="L20" s="62">
+        <v>3.175430900252172E-2</v>
+      </c>
+      <c r="M20" s="62">
+        <v>2.3941670520794517E-2</v>
+      </c>
+      <c r="N20" s="62">
+        <v>2.2404806053620874E-2</v>
+      </c>
+      <c r="O20" s="62">
+        <v>2.4330559242366954E-2</v>
+      </c>
+      <c r="P20" s="62">
+        <v>3.0816985426270229E-2</v>
+      </c>
+      <c r="Q20" s="62">
+        <v>3.4381201363687525E-2</v>
+      </c>
+      <c r="R20" s="63">
         <v>36434</v>
       </c>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-    </row>
-    <row r="21" spans="1:22" ht="18" customHeight="1">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-    </row>
-    <row r="22" spans="1:22" ht="35.1" customHeight="1">
-      <c r="B22" s="13"/>
-      <c r="C22" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="74"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="S22" s="13"/>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="B23" s="13"/>
-      <c r="C23" s="19" t="s">
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+    </row>
+    <row r="21" spans="1:24" ht="18" customHeight="1">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+    </row>
+    <row r="22" spans="1:24" ht="35.15" customHeight="1">
+      <c r="B22" s="14"/>
+      <c r="C22" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="75"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="B23" s="14"/>
+      <c r="C23" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="14"/>
+      <c r="V23" s="5"/>
+    </row>
+    <row r="24" spans="1:24" ht="36" customHeight="1">
+      <c r="B24" s="14"/>
+      <c r="C24" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="14"/>
+    </row>
+    <row r="25" spans="1:24" ht="17.25" customHeight="1">
+      <c r="C25" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" spans="1:24" ht="39" customHeight="1">
+      <c r="C26" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="13"/>
-    </row>
-    <row r="24" spans="1:22" ht="36" customHeight="1">
-      <c r="B24" s="13"/>
-      <c r="C24" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="S24" s="13"/>
-    </row>
-    <row r="25" spans="1:22" ht="17.25" customHeight="1">
-      <c r="C25" s="75" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-    </row>
-    <row r="26" spans="1:22" ht="39" customHeight="1">
-      <c r="C26" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="73"/>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="23"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="24"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-    </row>
-    <row r="29" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-    </row>
-    <row r="30" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
-    </row>
-    <row r="31" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-    </row>
-    <row r="32" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-    </row>
-    <row r="33" spans="3:18" ht="26.1" customHeight="1">
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
+    <row r="27" spans="1:24">
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="U28" s="7"/>
+    </row>
+    <row r="29" spans="1:24" ht="26.15" customHeight="1">
+      <c r="C29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+    </row>
+    <row r="30" spans="1:24" ht="26.15" customHeight="1">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+    </row>
+    <row r="31" spans="1:24" ht="26.15" customHeight="1">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+    </row>
+    <row r="32" spans="1:24" ht="26.15" customHeight="1">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+    </row>
+    <row r="33" spans="3:18" ht="26.15" customHeight="1">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
     </row>
     <row r="34" spans="3:18">
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
     </row>
     <row r="35" spans="3:18">
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
     </row>
     <row r="36" spans="3:18">
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
     </row>
     <row r="37" spans="3:18">
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
     </row>
     <row r="38" spans="3:18">
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
     </row>
     <row r="39" spans="3:18">
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="14"/>
+      <c r="Q39" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3110,7 +3337,7 @@
     <mergeCell ref="C24:R24"/>
     <mergeCell ref="C6:O6"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="E26:Q26">
     <cfRule type="cellIs" dxfId="4" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
@@ -3130,956 +3357,956 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V34"/>
-  <sheetFormatPr defaultColWidth="7.1640625" defaultRowHeight="12.95"/>
+  <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="0.1640625" style="12" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="3.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="17" width="11.33203125" customWidth="1"/>
-    <col min="18" max="18" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="0.19921875" style="13" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.796875" customWidth="1"/>
+    <col min="3" max="3" width="22.796875" customWidth="1"/>
+    <col min="4" max="4" width="14.796875" customWidth="1"/>
+    <col min="5" max="17" width="11.296875" customWidth="1"/>
+    <col min="18" max="18" width="2.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" hidden="1" customHeight="1">
-      <c r="C1" s="10">
-        <v>46265</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11">
+        <v>46295</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.95" hidden="1" customHeight="1">
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-    </row>
-    <row r="4" spans="1:19" ht="95.1" customHeight="1"/>
-    <row r="5" spans="1:19" ht="71.099999999999994" customHeight="1">
-      <c r="B5" s="12"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-    </row>
-    <row r="6" spans="1:19" ht="18.95" customHeight="1">
-      <c r="B6" s="12"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" ht="19" hidden="1" customHeight="1">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+    </row>
+    <row r="4" spans="1:19" ht="95.15" customHeight="1"/>
+    <row r="5" spans="1:19" ht="71.150000000000006" customHeight="1">
+      <c r="B5" s="13"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+    </row>
+    <row r="6" spans="1:19" ht="19" customHeight="1">
+      <c r="B6" s="13"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1">
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
     </row>
     <row r="8" spans="1:19" ht="21">
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="73"/>
+    </row>
+    <row r="9" spans="1:19" s="31" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="30"/>
+      <c r="C9" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+    </row>
+    <row r="10" spans="1:19" ht="13" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="53">
+        <v>3883.4871752899999</v>
+      </c>
+      <c r="E10" s="54">
+        <v>-7.2161352725853105E-3</v>
+      </c>
+      <c r="F10" s="54">
+        <v>1.1632982912133306E-2</v>
+      </c>
+      <c r="G10" s="54">
+        <v>8.7057158563388318E-2</v>
+      </c>
+      <c r="H10" s="54">
+        <v>1.1632982912133306E-2</v>
+      </c>
+      <c r="I10" s="54">
+        <v>8.855054778215761E-2</v>
+      </c>
+      <c r="J10" s="54">
+        <v>0.10864553102288466</v>
+      </c>
+      <c r="K10" s="54">
+        <v>0.1234923699334884</v>
+      </c>
+      <c r="L10" s="54">
+        <v>8.2615600892563396E-2</v>
+      </c>
+      <c r="M10" s="54">
+        <v>9.4798269187625003E-2</v>
+      </c>
+      <c r="N10" s="54">
+        <v>0.10223471880064319</v>
+      </c>
+      <c r="O10" s="54">
+        <v>0.11278033326115269</v>
+      </c>
+      <c r="P10" s="54">
+        <v>8.0934068992163821E-2</v>
+      </c>
+      <c r="Q10" s="42">
+        <v>39448</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="13" customHeight="1">
+      <c r="A11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="57">
+        <v>38391.731488080004</v>
+      </c>
+      <c r="E11" s="58">
+        <v>-5.6526245313531084E-3</v>
+      </c>
+      <c r="F11" s="58">
+        <v>7.9070623072765977E-3</v>
+      </c>
+      <c r="G11" s="58">
+        <v>7.1926131611897023E-2</v>
+      </c>
+      <c r="H11" s="58">
+        <v>7.9070623072765977E-3</v>
+      </c>
+      <c r="I11" s="58">
+        <v>7.3940293677805483E-2</v>
+      </c>
+      <c r="J11" s="58">
+        <v>9.1826925728821132E-2</v>
+      </c>
+      <c r="K11" s="58">
+        <v>0.10484243137650838</v>
+      </c>
+      <c r="L11" s="58">
+        <v>6.9486682464287866E-2</v>
+      </c>
+      <c r="M11" s="58">
+        <v>7.9586075878450194E-2</v>
+      </c>
+      <c r="N11" s="58">
+        <v>8.8990016655109236E-2</v>
+      </c>
+      <c r="O11" s="58">
+        <v>0.10006091288689181</v>
+      </c>
+      <c r="P11" s="58">
+        <v>7.5812128158087452E-2</v>
+      </c>
+      <c r="Q11" s="43">
+        <v>39448</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="13" customHeight="1">
+      <c r="A12" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="P8" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="72"/>
-    </row>
-    <row r="9" spans="1:19" s="30" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="29"/>
-      <c r="C9" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-    </row>
-    <row r="10" spans="1:19" ht="12.95" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="C12" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="59">
+        <v>885.49728098000003</v>
+      </c>
+      <c r="E12" s="60">
+        <v>-1.1847696683507151E-2</v>
+      </c>
+      <c r="F12" s="60">
+        <v>-5.3495425858847302E-3</v>
+      </c>
+      <c r="G12" s="60">
+        <v>7.694639458004629E-2</v>
+      </c>
+      <c r="H12" s="60">
+        <v>-5.3495425858847302E-3</v>
+      </c>
+      <c r="I12" s="60">
+        <v>5.0525076518374151E-2</v>
+      </c>
+      <c r="J12" s="60">
+        <v>8.0976644582696017E-2</v>
+      </c>
+      <c r="K12" s="60">
+        <v>0.10063294794582926</v>
+      </c>
+      <c r="L12" s="60">
+        <v>6.1422232612104742E-2</v>
+      </c>
+      <c r="M12" s="60">
+        <v>6.9980145725085E-2</v>
+      </c>
+      <c r="N12" s="60">
+        <v>7.95867039274369E-2</v>
+      </c>
+      <c r="O12" s="60">
+        <v>9.4444645040052358E-2</v>
+      </c>
+      <c r="P12" s="60">
+        <v>7.136002753753877E-2</v>
+      </c>
+      <c r="Q12" s="44">
+        <v>39448</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="12.65" customHeight="1">
+      <c r="A13" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="52">
-        <v>3862.4976410100003</v>
-      </c>
-      <c r="E10" s="53">
-        <v>1.3224085819194724E-2</v>
-      </c>
-      <c r="F10" s="53">
-        <v>3.3533800429872064E-2</v>
-      </c>
-      <c r="G10" s="53">
-        <v>5.0687837248314591E-2</v>
-      </c>
-      <c r="H10" s="53">
-        <v>1.8986124628338874E-2</v>
-      </c>
-      <c r="I10" s="53">
-        <v>0.11138100375568363</v>
-      </c>
-      <c r="J10" s="53">
-        <v>0.11849338692740644</v>
-      </c>
-      <c r="K10" s="53">
-        <v>0.11877946060588226</v>
-      </c>
-      <c r="L10" s="53">
-        <v>8.1051995286640657E-2</v>
-      </c>
-      <c r="M10" s="53">
-        <v>9.7710513600768989E-2</v>
-      </c>
-      <c r="N10" s="53">
-        <v>0.10352906271648753</v>
-      </c>
-      <c r="O10" s="53">
-        <v>0.11101729920923115</v>
-      </c>
-      <c r="P10" s="53">
-        <v>8.1723607913009505E-2</v>
-      </c>
-      <c r="Q10" s="41">
+      <c r="C13" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="57">
+        <v>2243.0427038299999</v>
+      </c>
+      <c r="E13" s="58">
+        <v>-3.687861191288673E-3</v>
+      </c>
+      <c r="F13" s="58">
+        <v>8.083173560409199E-3</v>
+      </c>
+      <c r="G13" s="58">
+        <v>8.2725835300054645E-2</v>
+      </c>
+      <c r="H13" s="58">
+        <v>8.083173560409199E-3</v>
+      </c>
+      <c r="I13" s="58">
+        <v>6.361008796920363E-2</v>
+      </c>
+      <c r="J13" s="58">
+        <v>9.7305465041110414E-2</v>
+      </c>
+      <c r="K13" s="58">
+        <v>0.1256510536780632</v>
+      </c>
+      <c r="L13" s="58">
+        <v>8.0792953852153043E-2</v>
+      </c>
+      <c r="M13" s="58">
+        <v>8.6269026975228105E-2</v>
+      </c>
+      <c r="N13" s="58">
+        <v>9.0605538912961803E-2</v>
+      </c>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58">
+        <v>9.2687806067174597E-2</v>
+      </c>
+      <c r="Q13" s="45">
+        <v>40849</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="13" customHeight="1">
+      <c r="A14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="59">
+        <v>9475.5450680599988</v>
+      </c>
+      <c r="E14" s="60">
+        <v>-5.6956356389499894E-3</v>
+      </c>
+      <c r="F14" s="60">
+        <v>4.0891459946753757E-3</v>
+      </c>
+      <c r="G14" s="60">
+        <v>5.8801109916995734E-2</v>
+      </c>
+      <c r="H14" s="60">
+        <v>4.0891459946753757E-3</v>
+      </c>
+      <c r="I14" s="60">
+        <v>6.1088804749060713E-2</v>
+      </c>
+      <c r="J14" s="60">
+        <v>7.8655157232559197E-2</v>
+      </c>
+      <c r="K14" s="60">
+        <v>8.8316082403614285E-2</v>
+      </c>
+      <c r="L14" s="60">
+        <v>5.4732069284125037E-2</v>
+      </c>
+      <c r="M14" s="60">
+        <v>6.1820159723016611E-2</v>
+      </c>
+      <c r="N14" s="60">
+        <v>7.0341622166971651E-2</v>
+      </c>
+      <c r="O14" s="60">
+        <v>8.2659619377414631E-2</v>
+      </c>
+      <c r="P14" s="60">
+        <v>6.8296138836423811E-2</v>
+      </c>
+      <c r="Q14" s="44">
         <v>39448</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="12.95" customHeight="1">
-      <c r="A11" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="56">
-        <v>38284.813427230001</v>
-      </c>
-      <c r="E11" s="57">
-        <v>9.9421552755779123E-3</v>
-      </c>
-      <c r="F11" s="57">
-        <v>2.8533931626304011E-2</v>
-      </c>
-      <c r="G11" s="57">
-        <v>4.3186744183812402E-2</v>
-      </c>
-      <c r="H11" s="57">
-        <v>1.3636770381416127E-2</v>
-      </c>
-      <c r="I11" s="57">
-        <v>9.2886237073877623E-2</v>
-      </c>
-      <c r="J11" s="57">
-        <v>0.10055292035133201</v>
-      </c>
-      <c r="K11" s="57">
-        <v>0.10070054474897744</v>
-      </c>
-      <c r="L11" s="57">
-        <v>6.8680571717400385E-2</v>
-      </c>
-      <c r="M11" s="57">
-        <v>8.183936908109346E-2</v>
-      </c>
-      <c r="N11" s="57">
-        <v>9.0075463405551656E-2</v>
-      </c>
-      <c r="O11" s="57">
-        <v>9.8920795107310583E-2</v>
-      </c>
-      <c r="P11" s="57">
-        <v>7.6484734578543365E-2</v>
-      </c>
-      <c r="Q11" s="42">
+    <row r="15" spans="1:19" ht="13" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="67">
+        <v>4492.3558580200006</v>
+      </c>
+      <c r="E15" s="68">
+        <v>-6.2053894727270159E-3</v>
+      </c>
+      <c r="F15" s="68">
+        <v>-9.0081984034750748E-4</v>
+      </c>
+      <c r="G15" s="68">
+        <v>4.05375725253894E-2</v>
+      </c>
+      <c r="H15" s="68">
+        <v>-9.0081984034750748E-4</v>
+      </c>
+      <c r="I15" s="68">
+        <v>4.4267277653791987E-2</v>
+      </c>
+      <c r="J15" s="68">
+        <v>5.9979440176156716E-2</v>
+      </c>
+      <c r="K15" s="68">
+        <v>6.7743172470974111E-2</v>
+      </c>
+      <c r="L15" s="68">
+        <v>3.9950726192995993E-2</v>
+      </c>
+      <c r="M15" s="68">
+        <v>4.2800514858397386E-2</v>
+      </c>
+      <c r="N15" s="68">
+        <v>5.1674415949414514E-2</v>
+      </c>
+      <c r="O15" s="68">
+        <v>6.3148245068707656E-2</v>
+      </c>
+      <c r="P15" s="68">
+        <v>5.8050350932996715E-2</v>
+      </c>
+      <c r="Q15" s="46">
         <v>39448</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="12.95" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="58">
-        <v>901.08665222000002</v>
-      </c>
-      <c r="E12" s="59">
-        <v>8.6681391152242607E-3</v>
-      </c>
-      <c r="F12" s="59">
-        <v>2.5180612349701363E-2</v>
-      </c>
-      <c r="G12" s="59">
-        <v>3.691160783582375E-2</v>
-      </c>
-      <c r="H12" s="59">
-        <v>6.5760653249635178E-3</v>
-      </c>
-      <c r="I12" s="59">
-        <v>7.6777802562231462E-2</v>
-      </c>
-      <c r="J12" s="59">
-        <v>9.198118993075223E-2</v>
-      </c>
-      <c r="K12" s="59">
-        <v>9.7608993156289306E-2</v>
-      </c>
-      <c r="L12" s="59">
-        <v>6.1719112767720755E-2</v>
-      </c>
-      <c r="M12" s="59">
-        <v>7.3567042995943729E-2</v>
-      </c>
-      <c r="N12" s="59">
-        <v>8.1064797865948682E-2</v>
-      </c>
-      <c r="O12" s="59">
-        <v>9.4121732223593393E-2</v>
-      </c>
-      <c r="P12" s="59">
-        <v>7.2369022911127706E-2</v>
-      </c>
-      <c r="Q12" s="43">
+    <row r="16" spans="1:19" s="31" customFormat="1" ht="14.15" customHeight="1">
+      <c r="A16" s="30"/>
+      <c r="C16" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="34"/>
+    </row>
+    <row r="17" spans="1:22" ht="13" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="53">
+        <v>1978.70736068</v>
+      </c>
+      <c r="E17" s="54">
+        <v>-3.2757539700670794E-2</v>
+      </c>
+      <c r="F17" s="54">
+        <v>1.0540268513563269E-2</v>
+      </c>
+      <c r="G17" s="54">
+        <v>5.0262607934202549E-2</v>
+      </c>
+      <c r="H17" s="54">
+        <v>1.0540268513563269E-2</v>
+      </c>
+      <c r="I17" s="54">
+        <v>6.6916813085999324E-2</v>
+      </c>
+      <c r="J17" s="54">
+        <v>9.4231550600764311E-2</v>
+      </c>
+      <c r="K17" s="54">
+        <v>0.13367567438533046</v>
+      </c>
+      <c r="L17" s="54">
+        <v>0.10423541589613745</v>
+      </c>
+      <c r="M17" s="54">
+        <v>0.10607987684400763</v>
+      </c>
+      <c r="N17" s="54">
+        <v>0.1120725458163175</v>
+      </c>
+      <c r="O17" s="54">
+        <v>0.12072413267842511</v>
+      </c>
+      <c r="P17" s="54">
+        <v>8.5276049054022057E-2</v>
+      </c>
+      <c r="Q17" s="56">
         <v>39448</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="12.6" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="56">
-        <v>2231.7921499099998</v>
-      </c>
-      <c r="E13" s="57">
-        <v>9.1585106961653388E-3</v>
-      </c>
-      <c r="F13" s="57">
-        <v>2.5473278891754873E-2</v>
-      </c>
-      <c r="G13" s="57">
-        <v>4.2070437395442084E-2</v>
-      </c>
-      <c r="H13" s="57">
-        <v>1.1814605376355725E-2</v>
-      </c>
-      <c r="I13" s="57">
-        <v>7.7191429417481944E-2</v>
-      </c>
-      <c r="J13" s="57">
-        <v>0.10641880554451065</v>
-      </c>
-      <c r="K13" s="57">
-        <v>0.11721198511484207</v>
-      </c>
-      <c r="L13" s="57">
-        <v>7.6994951254255928E-2</v>
-      </c>
-      <c r="M13" s="57">
-        <v>8.8976597921386638E-2</v>
-      </c>
-      <c r="N13" s="57">
-        <v>9.0573345938289931E-2</v>
-      </c>
-      <c r="O13" s="57"/>
-      <c r="P13" s="57">
-        <v>9.3496531523454315E-2</v>
-      </c>
-      <c r="Q13" s="44">
-        <v>40849</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="12.95" customHeight="1">
-      <c r="A14" s="12" t="s">
+    <row r="18" spans="1:22" ht="13" customHeight="1">
+      <c r="A18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="58">
-        <v>9495.6024483300007</v>
-      </c>
-      <c r="E14" s="59">
-        <v>7.7796087634850984E-3</v>
-      </c>
-      <c r="F14" s="59">
-        <v>2.3495423199711249E-2</v>
-      </c>
-      <c r="G14" s="59">
-        <v>3.6496655284232453E-2</v>
-      </c>
-      <c r="H14" s="59">
-        <v>9.8408314237996581E-3</v>
-      </c>
-      <c r="I14" s="59">
-        <v>7.8444806545094378E-2</v>
-      </c>
-      <c r="J14" s="59">
-        <v>8.6660083497126256E-2</v>
-      </c>
-      <c r="K14" s="59">
-        <v>8.5236908488632385E-2</v>
-      </c>
-      <c r="L14" s="59">
-        <v>5.4246550638852975E-2</v>
-      </c>
-      <c r="M14" s="59">
-        <v>6.3474059306860925E-2</v>
-      </c>
-      <c r="N14" s="59">
-        <v>7.135932235389944E-2</v>
-      </c>
-      <c r="O14" s="59">
-        <v>8.1907010404830075E-2</v>
-      </c>
-      <c r="P14" s="59">
-        <v>6.8933546020515726E-2</v>
-      </c>
-      <c r="Q14" s="43">
+      <c r="C18" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="57">
+        <v>1771.5512075300001</v>
+      </c>
+      <c r="E18" s="58">
+        <v>1.7247876765708006E-2</v>
+      </c>
+      <c r="F18" s="58">
+        <v>1.4819812195059781E-2</v>
+      </c>
+      <c r="G18" s="58">
+        <v>0.15038845621316704</v>
+      </c>
+      <c r="H18" s="58">
+        <v>1.4819812195059781E-2</v>
+      </c>
+      <c r="I18" s="58">
+        <v>0.10446431141606186</v>
+      </c>
+      <c r="J18" s="58">
+        <v>0.15670385744142382</v>
+      </c>
+      <c r="K18" s="58">
+        <v>0.17330508245793877</v>
+      </c>
+      <c r="L18" s="58">
+        <v>0.10090688261021105</v>
+      </c>
+      <c r="M18" s="58">
+        <v>0.12778396055223393</v>
+      </c>
+      <c r="N18" s="58">
+        <v>0.13338915979915028</v>
+      </c>
+      <c r="O18" s="58">
+        <v>0.14319818522383759</v>
+      </c>
+      <c r="P18" s="58">
+        <v>9.2198212090883441E-2</v>
+      </c>
+      <c r="Q18" s="45">
         <v>39448</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="12.95" customHeight="1">
-      <c r="A15" s="12" t="s">
+    <row r="19" spans="1:22" ht="13" customHeight="1">
+      <c r="A19" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="66">
-        <v>4478.7735929099999</v>
-      </c>
-      <c r="E15" s="67">
-        <v>4.9527063048359883E-3</v>
-      </c>
-      <c r="F15" s="67">
-        <v>1.6933383445361019E-2</v>
-      </c>
-      <c r="G15" s="67">
-        <v>2.6181491084302136E-2</v>
-      </c>
-      <c r="H15" s="67">
-        <v>5.3376920906877201E-3</v>
-      </c>
-      <c r="I15" s="67">
-        <v>5.9768362983142739E-2</v>
-      </c>
-      <c r="J15" s="67">
-        <v>6.7411092103453155E-2</v>
-      </c>
-      <c r="K15" s="67">
-        <v>6.6001203141237599E-2</v>
-      </c>
-      <c r="L15" s="67">
-        <v>4.0211787740375662E-2</v>
-      </c>
-      <c r="M15" s="67">
-        <v>4.4088569231584759E-2</v>
-      </c>
-      <c r="N15" s="67">
-        <v>5.265588465497504E-2</v>
-      </c>
-      <c r="O15" s="67">
-        <v>6.3257219658922476E-2</v>
-      </c>
-      <c r="P15" s="67">
-        <v>5.8665816342335836E-2</v>
-      </c>
-      <c r="Q15" s="45">
+      <c r="C19" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="59">
+        <v>584.63877172000002</v>
+      </c>
+      <c r="E19" s="60">
+        <v>-1.3151795203926024E-2</v>
+      </c>
+      <c r="F19" s="60">
+        <v>-2.0280387117859844E-2</v>
+      </c>
+      <c r="G19" s="60">
+        <v>1.3822829682459546E-3</v>
+      </c>
+      <c r="H19" s="60">
+        <v>-2.0280387117859844E-2</v>
+      </c>
+      <c r="I19" s="60">
+        <v>-3.6089745781427915E-3</v>
+      </c>
+      <c r="J19" s="60">
+        <v>1.7599095069423847E-2</v>
+      </c>
+      <c r="K19" s="60">
+        <v>3.0382453343631152E-2</v>
+      </c>
+      <c r="L19" s="60">
+        <v>6.9186927733566068E-3</v>
+      </c>
+      <c r="M19" s="60">
+        <v>8.9972209135079102E-3</v>
+      </c>
+      <c r="N19" s="60">
+        <v>1.9467612217127533E-2</v>
+      </c>
+      <c r="O19" s="60">
+        <v>3.6453798779098032E-2</v>
+      </c>
+      <c r="P19" s="60">
+        <v>4.5852189814872664E-2</v>
+      </c>
+      <c r="Q19" s="44">
         <v>39448</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="30" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A16" s="29"/>
-      <c r="C16" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="33"/>
-    </row>
-    <row r="17" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A17" s="12" t="s">
+    <row r="20" spans="1:22" ht="13" customHeight="1">
+      <c r="A20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="52">
-        <v>2050.4135632900002</v>
-      </c>
-      <c r="E17" s="53">
-        <v>2.396368141977287E-2</v>
-      </c>
-      <c r="F17" s="53">
-        <v>4.9059249260494299E-2</v>
-      </c>
-      <c r="G17" s="53">
-        <v>1.9640847304099776E-2</v>
-      </c>
-      <c r="H17" s="53">
-        <v>4.4764172367737907E-2</v>
-      </c>
-      <c r="I17" s="53">
-        <v>0.1044949776950439</v>
-      </c>
-      <c r="J17" s="53">
-        <v>0.12831785266536266</v>
-      </c>
-      <c r="K17" s="53">
-        <v>0.13802643544285811</v>
-      </c>
-      <c r="L17" s="53">
-        <v>0.10915903412928539</v>
-      </c>
-      <c r="M17" s="53">
-        <v>0.11495038231509647</v>
-      </c>
-      <c r="N17" s="53">
-        <v>0.11689930601437082</v>
-      </c>
-      <c r="O17" s="53">
-        <v>0.11851302680547909</v>
-      </c>
-      <c r="P17" s="53">
-        <v>8.7604413342052628E-2</v>
-      </c>
-      <c r="Q17" s="55">
+      <c r="C20" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="61">
+        <v>3827.48263791</v>
+      </c>
+      <c r="E20" s="62">
+        <v>3.8639874743701943E-3</v>
+      </c>
+      <c r="F20" s="62">
+        <v>1.2230606884233747E-2</v>
+      </c>
+      <c r="G20" s="62">
+        <v>2.4537952918486004E-2</v>
+      </c>
+      <c r="H20" s="62">
+        <v>1.2230606884233747E-2</v>
+      </c>
+      <c r="I20" s="62">
+        <v>4.5486047789455544E-2</v>
+      </c>
+      <c r="J20" s="62">
+        <v>4.6533420900821319E-2</v>
+      </c>
+      <c r="K20" s="62">
+        <v>4.7087325201426701E-2</v>
+      </c>
+      <c r="L20" s="62">
+        <v>3.6883057457889501E-2</v>
+      </c>
+      <c r="M20" s="62">
+        <v>2.7809236317133508E-2</v>
+      </c>
+      <c r="N20" s="62">
+        <v>2.6145222432769039E-2</v>
+      </c>
+      <c r="O20" s="62">
+        <v>2.8415933806133449E-2</v>
+      </c>
+      <c r="P20" s="62">
+        <v>3.3436163010020815E-2</v>
+      </c>
+      <c r="Q20" s="63">
         <v>39448</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A18" s="12" t="s">
+    <row r="21" spans="1:22" ht="18" customHeight="1">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+    </row>
+    <row r="22" spans="1:22" s="18" customFormat="1" ht="26.15" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="56">
-        <v>1728.4879569300001</v>
-      </c>
-      <c r="E18" s="57">
-        <v>3.4539705542261279E-3</v>
-      </c>
-      <c r="F18" s="57">
-        <v>3.1467043035322544E-2</v>
-      </c>
-      <c r="G18" s="57">
-        <v>8.706463517905659E-2</v>
-      </c>
-      <c r="H18" s="57">
-        <v>-2.3868956879695273E-3</v>
-      </c>
-      <c r="I18" s="57">
-        <v>0.10972909743687127</v>
-      </c>
-      <c r="J18" s="57">
-        <v>0.14284280021564827</v>
-      </c>
-      <c r="K18" s="57">
-        <v>0.15173007968092567</v>
-      </c>
-      <c r="L18" s="57">
-        <v>9.0563747175518711E-2</v>
-      </c>
-      <c r="M18" s="57">
-        <v>0.12598534037810488</v>
-      </c>
-      <c r="N18" s="57">
-        <v>0.13060241409182127</v>
-      </c>
-      <c r="O18" s="57">
-        <v>0.14099166605013952</v>
-      </c>
-      <c r="P18" s="57">
-        <v>9.1622304180603589E-2</v>
-      </c>
-      <c r="Q18" s="44">
-        <v>39448</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A19" s="12" t="s">
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="79"/>
+    </row>
+    <row r="23" spans="1:22" s="18" customFormat="1" ht="2.5" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="79"/>
+    </row>
+    <row r="24" spans="1:22" s="18" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="79"/>
+      <c r="Q24" s="79"/>
+    </row>
+    <row r="25" spans="1:22" s="18" customFormat="1" ht="12.5">
+      <c r="A25" s="17"/>
+      <c r="B25" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
+    </row>
+    <row r="26" spans="1:22" s="18" customFormat="1" ht="41.5" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="64" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="58">
-        <v>594.79834009000001</v>
-      </c>
-      <c r="E19" s="59">
-        <v>-8.5418189780066554E-5</v>
-      </c>
-      <c r="F19" s="59">
-        <v>3.4157536718803551E-4</v>
-      </c>
-      <c r="G19" s="59">
-        <v>-3.5593246142485275E-3</v>
-      </c>
-      <c r="H19" s="59">
-        <v>-7.2235951580890802E-3</v>
-      </c>
-      <c r="I19" s="59">
-        <v>1.3722242998679567E-2</v>
-      </c>
-      <c r="J19" s="59">
-        <v>2.7021788431249416E-2</v>
-      </c>
-      <c r="K19" s="59">
-        <v>3.3605228243211896E-2</v>
-      </c>
-      <c r="L19" s="59">
-        <v>9.307925668645068E-3</v>
-      </c>
-      <c r="M19" s="59">
-        <v>1.0693942523812391E-2</v>
-      </c>
-      <c r="N19" s="59">
-        <v>2.1036261283610427E-2</v>
-      </c>
-      <c r="O19" s="59">
-        <v>3.8765575507725317E-2</v>
-      </c>
-      <c r="P19" s="59">
-        <v>4.6800177405979505E-2</v>
-      </c>
-      <c r="Q19" s="43">
-        <v>39448</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="12.95" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="60">
-        <v>3548.8766306500002</v>
-      </c>
-      <c r="E20" s="61">
-        <v>4.2594429820847724E-3</v>
-      </c>
-      <c r="F20" s="61">
-        <v>1.2722527550434929E-2</v>
-      </c>
-      <c r="G20" s="61">
-        <v>2.4175288680767321E-2</v>
-      </c>
-      <c r="H20" s="61">
-        <v>8.3344153334090603E-3</v>
-      </c>
-      <c r="I20" s="61">
-        <v>4.5133776572813547E-2</v>
-      </c>
-      <c r="J20" s="61">
-        <v>4.6631218356770879E-2</v>
-      </c>
-      <c r="K20" s="61">
-        <v>4.7003647375651582E-2</v>
-      </c>
-      <c r="L20" s="61">
-        <v>3.6124430703919512E-2</v>
-      </c>
-      <c r="M20" s="61">
-        <v>2.7436412093498428E-2</v>
-      </c>
-      <c r="N20" s="61">
-        <v>2.5936470869448745E-2</v>
-      </c>
-      <c r="O20" s="61">
-        <v>2.8429286793702307E-2</v>
-      </c>
-      <c r="P20" s="61">
-        <v>3.3372358449103134E-2</v>
-      </c>
-      <c r="Q20" s="62">
-        <v>39448</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="18" customHeight="1">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-    </row>
-    <row r="22" spans="1:22" s="17" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="78" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-    </row>
-    <row r="23" spans="1:22" s="17" customFormat="1" ht="2.4500000000000002" customHeight="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-    </row>
-    <row r="24" spans="1:22" s="17" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="78" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
-    </row>
-    <row r="25" spans="1:22" s="17" customFormat="1" ht="12.6">
-      <c r="A25" s="16"/>
-      <c r="B25" s="79" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
-      <c r="Q25" s="79"/>
-    </row>
-    <row r="26" spans="1:22" s="17" customFormat="1" ht="41.45" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="80"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="81"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
     </row>
     <row r="27" spans="1:22" ht="39" customHeight="1">
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
-      <c r="M27" s="77"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="77"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="78"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="78"/>
+      <c r="N27" s="78"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="78"/>
+      <c r="Q27" s="78"/>
       <c r="R27" s="1"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="71"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="77"/>
-    </row>
-    <row r="30" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
-      <c r="M30" s="81"/>
-      <c r="N30" s="81"/>
-      <c r="O30" s="81"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-    </row>
-    <row r="31" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-    </row>
-    <row r="32" spans="1:22" ht="26.1" customHeight="1">
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="81"/>
-      <c r="N32" s="81"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-    </row>
-    <row r="33" spans="3:17" ht="26.1" customHeight="1">
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="81"/>
-      <c r="N33" s="81"/>
-      <c r="O33" s="81"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-    </row>
-    <row r="34" spans="3:17" ht="26.1" customHeight="1"/>
+      <c r="T29" s="78"/>
+      <c r="U29" s="78"/>
+      <c r="V29" s="78"/>
+    </row>
+    <row r="30" spans="1:22" ht="26.15" customHeight="1">
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+    </row>
+    <row r="31" spans="1:22" ht="26.15" customHeight="1">
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
+      <c r="M31" s="82"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+    </row>
+    <row r="32" spans="1:22" ht="26.15" customHeight="1">
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="82"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+    </row>
+    <row r="33" spans="3:17" ht="26.15" customHeight="1">
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+    </row>
+    <row r="34" spans="3:17" ht="26.15" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="T29:V29"/>
@@ -4127,65 +4354,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005DC95613170AD541A1ACA0E893584A98" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b58b6af8c26e0dae27f7873f3072402">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="05c3b009-07a7-41e1-9067-dad62aaf44d0" xmlns:ns3="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns5="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa8d5a8e80a87f753beebba1ea9c5782" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4540,16 +4708,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <TaxCatchAll xmlns="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff" xsi:nil="true"/>
-    <_dlc_DocId xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">MEM020-1928282007-985978</_dlc_DocId>
+    <_dlc_DocId xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">MEM020-1928282007-990181</_dlc_DocId>
     <_dlc_DocIdUrl xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">
-      <Url>https://australiansuper.sharepoint.com/teams/MEMMarketing/_layouts/15/DocIdRedir.aspx?ID=MEM020-1928282007-985978</Url>
-      <Description>MEM020-1928282007-985978</Description>
+      <Url>https://australiansuper.sharepoint.com/teams/MEMMarketing/_layouts/15/DocIdRedir.aspx?ID=MEM020-1928282007-990181</Url>
+      <Description>MEM020-1928282007-990181</Description>
     </_dlc_DocIdUrl>
     <SharedWithUsers xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">
       <UserInfo>
@@ -4598,20 +4766,124 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D7DB65-0DC2-4D64-A74D-4D73CCCADE99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1455F7E-852C-4114-9EB7-F625C5184352}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="05c3b009-07a7-41e1-9067-dad62aaf44d0"/>
+    <ds:schemaRef ds:uri="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F1476A-B5B9-40EF-A53E-6CD6A17FAC54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A0CFC47-C21A-4C13-ADDE-45F0CE497741}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c5064bf2-310c-4cc7-a1bf-7de2b6fc5997"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="eaf2e70e-2c74-47e4-9f5b-aeff8bab5ce2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="21a346d0-3dae-4461-adad-337d1039f7e7"/>
+    <ds:schemaRef ds:uri="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff"/>
+    <ds:schemaRef ds:uri="05c3b009-07a7-41e1-9067-dad62aaf44d0"/>
+    <ds:schemaRef ds:uri="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB1726D-1DA2-4081-82C6-D43A4CB65EFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D7DB65-0DC2-4D64-A74D-4D73CCCADE99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A0CFC47-C21A-4C13-ADDE-45F0CE497741}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F1476A-B5B9-40EF-A53E-6CD6A17FAC54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
